--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -741,14 +741,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -775,17 +774,27 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
@@ -797,8 +806,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12278
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -809,7 +817,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -820,13 +829,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -838,13 +847,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -870,7 +879,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -888,7 +897,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -912,43 +921,43 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8235
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
@@ -960,19 +969,19 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -984,7 +993,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -996,13 +1005,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -1046,13 +1055,13 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1068,10 +1077,16 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1088,13 +1103,13 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>471</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1117,13 +1132,13 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1135,11 +1150,16 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -1174,7 +1194,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1186,16 +1206,11 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -1204,43 +1219,44 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">54621561
+81
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11092
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">283412
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -1252,13 +1268,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1270,13 +1286,12 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1319,19 +1334,19 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1341,16 +1356,21 @@
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1363,19 +1383,19 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1393,21 +1413,31 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">450
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1425,7 +1455,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11944
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1448,16 +1478,20 @@
           <t>1458</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1468,41 +1502,45 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1519,50 +1557,50 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>134</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>957</t>
+          <t xml:space="preserve">957
+</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1582,87 +1620,86 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1671,13 +1708,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1689,31 +1726,31 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1733,48 +1770,55 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1861
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1786,45 +1830,45 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>484</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -1836,19 +1880,18 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1879,7 +1922,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1891,7 +1934,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1903,49 +1946,49 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1963,7 +2006,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1981,7 +2024,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1993,7 +2036,8 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2018,19 +2062,19 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2042,13 +2086,13 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2060,10 +2104,16 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2072,64 +2122,64 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10660
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -2138,7 +2188,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2164,7 +2214,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2174,7 +2224,12 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -2189,103 +2244,102 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2462
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11182
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1393
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2311,139 +2365,137 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1646
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2463,25 +2515,30 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2492,41 +2549,43 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2537,29 +2596,29 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2571,18 +2630,18 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t xml:space="preserve">933
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -2614,12 +2673,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2631,7 +2691,8 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">113
+61
 </t>
         </is>
       </c>
@@ -2643,8 +2704,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>007</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2659,28 +2719,32 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2204
 </t>
         </is>
       </c>
@@ -2692,13 +2756,12 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2710,25 +2773,24 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2748,28 +2810,28 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -2780,91 +2842,94 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">060
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t xml:space="preserve">468
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>691</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t xml:space="preserve">469
+</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2883,97 +2948,98 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2985,7 +3051,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -2997,19 +3063,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3029,7 +3095,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3041,37 +3107,37 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3083,19 +3149,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8810
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -3119,48 +3185,49 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">24654
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3180,132 +3247,131 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>64170</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3343,126 +3409,124 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1880
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">2678
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">7268
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -3494,120 +3558,116 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>348</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2850
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>711</t>
+          <t xml:space="preserve">1114
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">967
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12385
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -3627,7 +3687,7 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3639,25 +3699,25 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3669,7 +3729,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3681,18 +3741,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3704,24 +3765,25 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>804</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3733,31 +3795,31 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3775,7 +3837,12 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1456
+</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3783,8 +3850,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3794,13 +3860,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3817,7 +3882,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3828,68 +3893,66 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -3915,84 +3978,88 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1309
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -4001,7 +4068,8 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -4018,13 +4086,13 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">144944
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4036,13 +4104,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4062,77 +4130,87 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>4654</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11946
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4153,7 +4231,7 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4171,7 +4249,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4203,19 +4281,19 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4227,19 +4305,19 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4251,23 +4329,28 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">34
@@ -4276,7 +4359,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4288,49 +4371,49 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2956
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4356,13 +4439,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4380,7 +4463,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4392,24 +4475,24 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4445,7 +4528,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -4457,7 +4540,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12296
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4469,13 +4552,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4501,25 +4584,25 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
+          <t xml:space="preserve">13532
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">858
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -4529,7 +4612,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4540,7 +4623,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4552,28 +4635,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>417</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
+          <t xml:space="preserve">1391
 </t>
         </is>
       </c>
@@ -4585,40 +4669,44 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>964</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>346</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4637,7 +4725,7 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4649,7 +4737,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4661,13 +4749,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8106
-</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -4677,10 +4764,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4691,55 +4783,50 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4751,19 +4838,19 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4783,7 +4870,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4807,74 +4894,75 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1924
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4886,7 +4974,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4904,7 +4992,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4936,13 +5024,13 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4954,25 +5042,25 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4990,25 +5078,25 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5020,44 +5108,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5077,7 +5170,7 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5089,13 +5182,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5107,7 +5200,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5119,7 +5212,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5131,19 +5224,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -5155,7 +5248,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5167,13 +5260,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">576
 </t>
         </is>
       </c>
@@ -5191,7 +5284,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5203,13 +5296,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5229,7 +5322,7 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5241,7 +5334,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5253,19 +5346,19 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -5277,7 +5370,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5287,10 +5380,15 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">9006
 </t>
         </is>
       </c>
@@ -5302,13 +5400,13 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -5320,43 +5418,43 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -5376,7 +5474,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">486
 </t>
         </is>
       </c>
@@ -5388,13 +5486,13 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5406,49 +5504,48 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5460,13 +5557,13 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5478,11 +5575,16 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -5497,13 +5599,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
@@ -5523,7 +5625,7 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
@@ -5535,14 +5637,13 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5553,13 +5654,13 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -5570,77 +5671,81 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t xml:space="preserve">999
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">19228
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="n"/>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3868
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -5666,59 +5771,60 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18950
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">7
+9
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5730,7 +5836,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">7378
 </t>
         </is>
       </c>
@@ -5742,55 +5848,56 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">77
+248
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">117
+203
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>00578</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5822,25 +5929,25 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5858,8 +5965,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5870,84 +5976,85 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122084
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2394
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5979,26 +6086,25 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6009,48 +6115,48 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11262
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2616
 </t>
         </is>
       </c>
@@ -6062,43 +6168,43 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1354
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6118,32 +6224,37 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6155,7 +6266,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6167,80 +6278,80 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">8401
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">765
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6260,55 +6371,55 @@
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1708
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -6320,25 +6431,25 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
@@ -6356,36 +6467,46 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6408,18 +6529,18 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6430,25 +6551,25 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -6460,7 +6581,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6472,31 +6593,31 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6508,7 +6629,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6520,17 +6641,22 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14270
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6547,18 +6673,27 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -6567,94 +6702,98 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">11256
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1650
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>7650</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1470
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -6678,42 +6817,42 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -6725,92 +6864,89 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">9984
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>0526</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01111
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">3179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6827,25 +6963,26 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">89
+6
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6867,10 +7004,15 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6882,79 +7024,81 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">2919292795
+24
+12
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -726,24 +726,54 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -751,18 +781,33 @@
         </is>
       </c>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="n"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1 39
+</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -772,9 +817,24 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
@@ -794,45 +854,105 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11289
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="n"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -850,7 +970,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -886,17 +1006,26 @@
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -906,52 +1035,87 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -995,22 +1159,43 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -1020,21 +1205,50 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11186
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
@@ -1044,7 +1258,12 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="3" t="n"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
@@ -1053,18 +1272,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1084,40 +1304,65 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n"/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1125,7 +1370,12 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
@@ -1134,26 +1384,31 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">450
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="n"/>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1180,30 +1435,44 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">824
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">346
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1214,18 +1483,25 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -1237,59 +1513,61 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">20991
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9926
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">2299
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">6150
 </t>
         </is>
       </c>
@@ -1309,119 +1587,138 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">113
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11026
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>2294610</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1439,98 +1736,114 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1284
+</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">1184
+</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
+          <t xml:space="preserve">8909
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+      <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1544,48 +1857,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11820
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -1595,64 +1935,64 @@
 </t>
         </is>
       </c>
-      <c r="P12" s="3" t="n"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1669,100 +2009,144 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 1
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11820
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">2835
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1780,70 +2164,105 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2868
+</t>
+        </is>
+      </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1855,26 +2274,30 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1892,86 +2315,135 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -1991,69 +2463,138 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+          <t xml:space="preserve">11988
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0909
+</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11139
+</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11910
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9006
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9808
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9200
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22812
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="n"/>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n"/>
+          <t xml:space="preserve">1528
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">3048
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2070,124 +2611,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">1001
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9106
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11282
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="n"/>
+          <t xml:space="preserve">522
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2993
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2204,90 +2763,140 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 1
+</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1804
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1146
+</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1604
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2304,74 +2913,133 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
+          <t xml:space="preserve">17 6
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29481
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11495
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2389,56 +3057,136 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11174
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
         </is>
       </c>
-      <c r="Y20" s="3" t="n"/>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2456,51 +3204,136 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9485
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="3" t="n"/>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590
+</t>
+        </is>
+      </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2518,60 +3351,136 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="n"/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2588,26 +3497,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1956
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n"/>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -2617,53 +3551,92 @@
 </t>
         </is>
       </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
+          <t xml:space="preserve">9268
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11804
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n"/>
+          <t xml:space="preserve">2679
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">22161
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2680,128 +3653,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19456
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t xml:space="preserve">281
+</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11034
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10804
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12678
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2818,99 +3805,129 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 1 5
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
+          <t xml:space="preserve">1028
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1569
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">12218
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n"/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="n"/>
       <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2924,70 +3941,149 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">385
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3001,51 +4097,97 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="n"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -3054,19 +4196,34 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="n"/>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -3083,52 +4240,127 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52940
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="n"/>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2207
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="n"/>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -3145,49 +4377,144 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n"/>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6595
+</t>
+        </is>
+      </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -3202,86 +4529,141 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19524
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18168
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n"/>
+          <t xml:space="preserve">20161
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26814
+</t>
+        </is>
+      </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">8365
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t xml:space="preserve">4200
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1320
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="n"/>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2989
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18182
+</t>
+        </is>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n"/>
-      <c r="Y30" s="3" t="n"/>
+          <t xml:space="preserve">9856
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3162
+</t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -3298,98 +4680,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13098
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28100
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">23183
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="n"/>
-      <c r="Y31" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3406,90 +4832,145 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
+          <t xml:space="preserve">2189
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">568
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3503,109 +4984,141 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t xml:space="preserve">286
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4200
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -3624,57 +5137,132 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n"/>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12846
+</t>
+        </is>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3690,60 +5278,135 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n"/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11908
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-      <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="n"/>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -3762,44 +5425,143 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n"/>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
-      <c r="T36" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="n"/>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3815,59 +5577,144 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8080
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218164
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10822
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="3" t="n"/>
-      <c r="S37" s="3" t="n"/>
+          <t xml:space="preserve">49208
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11022
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1098
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="3" t="n"/>
-      <c r="Z37" s="3" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1068
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3884,98 +5731,137 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11308
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8924208
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
+</t>
+        </is>
+      </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">387
+</t>
+        </is>
+      </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71481
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3989,94 +5875,141 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n"/>
+          <t xml:space="preserve">1026
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9421
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8986
+</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n"/>
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -4091,51 +6024,126 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -4144,13 +6152,13 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -4168,59 +6176,138 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8401
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="n"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623
+</t>
+        </is>
+      </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n"/>
+          <t xml:space="preserve">11084
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+          <t xml:space="preserve">765
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -4234,30 +6321,91 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>85401</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
-      <c r="Q42" s="3" t="n"/>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -4265,13 +6413,48 @@
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" s="3" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4286,54 +6469,143 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8094
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1299
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4350,58 +6622,74 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">8181
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11120
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
+          <t xml:space="preserve">1800
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4417,17 +6705,42 @@
 </t>
         </is>
       </c>
-      <c r="S44" s="3" t="n"/>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">470
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -4448,13 +6761,33 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0221
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2884
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
@@ -4466,7 +6799,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -4478,13 +6811,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">11896
 </t>
         </is>
       </c>
@@ -4494,8 +6827,18 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11027
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179926
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -4504,15 +6847,25 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16560
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">16620
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
@@ -4522,12 +6875,27 @@
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3228
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
@@ -4548,14 +6916,19 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n"/>
+          <t xml:space="preserve">2719
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4567,13 +6940,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4590,8 +6963,18 @@
 </t>
         </is>
       </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1854
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">831
@@ -4604,22 +6987,42 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -4628,13 +7031,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -726,12 +726,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
@@ -758,7 +753,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -780,10 +775,15 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -801,13 +801,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1 39
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -819,7 +819,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -904,13 +904,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -926,12 +926,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -952,7 +947,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -970,7 +965,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -982,7 +977,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -1008,7 +1003,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1055,7 +1050,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1079,7 +1074,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1169,12 +1164,7 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1195,7 +1185,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1207,13 +1197,14 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">074
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1228,7 +1219,12 @@
 </t>
         </is>
       </c>
-      <c r="P7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1243,12 +1239,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -1260,8 +1257,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1272,19 +1268,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1304,13 +1300,13 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1322,13 +1318,13 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1340,7 +1336,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1384,7 +1380,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">450
+          <t xml:space="preserve">459
 </t>
         </is>
       </c>
@@ -1396,7 +1392,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1445,15 +1441,10 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1152
-</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1465,13 +1456,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
@@ -1489,19 +1479,19 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -1513,49 +1503,49 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20991
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1567,7 +1557,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6150
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
@@ -1587,87 +1577,88 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1682,7 +1673,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1712,7 +1703,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
@@ -1738,14 +1729,12 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1756,8 +1745,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1768,8 +1756,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1792,7 +1779,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -1804,7 +1791,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8909
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1816,7 +1803,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1834,7 +1821,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
@@ -1857,15 +1844,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1925,7 +1907,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1943,13 +1925,13 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1961,7 +1943,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -1980,7 +1962,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -1992,7 +1974,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2009,94 +1991,91 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 1
-</t>
-        </is>
-      </c>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2835
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -2105,24 +2084,25 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -2140,16 +2120,10 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2178,20 +2152,14 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2202,7 +2170,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -2226,7 +2194,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -2244,7 +2212,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2868
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2256,7 +2224,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2268,7 +2236,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -2280,7 +2248,8 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>034</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2291,7 +2260,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2329,7 +2298,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2838
 </t>
         </is>
       </c>
@@ -2360,7 +2329,7 @@
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2378,13 +2347,14 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2463,16 +2433,11 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11988
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0909
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">11139
@@ -2487,22 +2452,21 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">906
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9006
-</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2511,8 +2475,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2523,36 +2486,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t xml:space="preserve">904
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22812
+          <t xml:space="preserve">8382
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -2570,31 +2528,30 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1528
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3048
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2611,15 +2568,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2643,7 +2595,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2668,7 +2620,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2680,13 +2632,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2698,7 +2650,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2716,7 +2668,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2728,19 +2680,18 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
@@ -2763,39 +2714,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 1
-</t>
-        </is>
-      </c>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2807,25 +2746,24 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2837,31 +2775,31 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">5298
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2879,8 +2817,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2910,7 +2847,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2931,13 +2873,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 6
+          <t xml:space="preserve">17 5
 </t>
         </is>
       </c>
@@ -2955,7 +2897,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -2967,7 +2909,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2979,14 +2921,13 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>701</t>
         </is>
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3004,18 +2945,19 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -3033,13 +2975,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3059,7 +3001,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3084,7 +3026,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3096,7 +3038,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3108,7 +3050,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3156,8 +3098,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3180,7 +3121,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -3206,7 +3147,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3218,7 +3159,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3242,19 +3183,19 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3266,7 +3207,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3297,13 +3238,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3321,13 +3262,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -3353,19 +3293,19 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3443,7 +3383,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3461,7 +3401,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3471,10 +3411,14 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="n"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3497,15 +3441,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3517,31 +3456,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">5295
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3553,7 +3491,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3565,49 +3503,48 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11804
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679
+          <t xml:space="preserve">82678
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3618,25 +3555,24 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22161
-</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3653,12 +3589,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
@@ -3673,19 +3604,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2375
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -3701,7 +3632,12 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -3758,7 +3694,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3776,7 +3712,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3805,26 +3741,22 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 1 5
-</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3836,13 +3768,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3854,46 +3786,41 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3902,8 +3829,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -3915,13 +3841,13 @@
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3943,7 +3869,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3955,37 +3881,37 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4007,14 +3933,10 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4050,13 +3972,12 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>438</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">2494
 </t>
         </is>
       </c>
@@ -4074,14 +3995,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4099,25 +4019,25 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4129,7 +4049,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4141,13 +4061,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4165,13 +4085,13 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4181,7 +4101,11 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="3" t="n"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4196,7 +4120,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -4242,17 +4166,22 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">94
@@ -4291,31 +4220,31 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52940
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4327,7 +4256,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4379,7 +4308,7 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4469,20 +4398,19 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4499,7 +4427,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4528,46 +4456,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19524
+          <t xml:space="preserve">13348
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18168
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20161
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26814
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -4585,25 +4518,23 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8365
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
-</t>
+          <t>434644</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4615,7 +4546,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -4633,38 +4564,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18182
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162
+          <t xml:space="preserve">31362
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4682,7 +4610,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4718,7 +4646,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4728,10 +4656,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85 2
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -4809,8 +4742,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
-</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4832,33 +4764,23 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4906,68 +4828,65 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>714</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1946
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n"/>
@@ -4984,21 +4903,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5022,13 +4936,13 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5046,13 +4960,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5064,19 +4978,18 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5106,7 +5019,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -5139,7 +5052,7 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5151,13 +5064,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -5205,7 +5118,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5217,13 +5130,13 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5247,7 +5160,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5259,7 +5172,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -5280,7 +5193,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5298,7 +5211,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5316,7 +5229,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5352,25 +5265,25 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11908
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5400,7 +5313,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5425,27 +5338,22 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5463,7 +5371,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5487,7 +5395,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
@@ -5535,7 +5443,8 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5579,13 +5488,13 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">8 82
 </t>
         </is>
       </c>
@@ -5597,62 +5506,60 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">4986
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8080
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218164
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5663,26 +5570,25 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>447</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5693,7 +5599,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5705,13 +5611,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1068
+          <t xml:space="preserve">1560
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -5767,13 +5673,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5785,7 +5691,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5821,13 +5727,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">387
+          <t xml:space="preserve">577
 </t>
         </is>
       </c>
@@ -5839,8 +5744,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -5875,126 +5779,116 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8986
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6006,7 +5900,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -6026,13 +5920,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6044,19 +5938,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3164
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6066,15 +5960,10 @@
 </t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
@@ -6104,19 +5993,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6128,7 +6017,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -6178,13 +6067,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -6202,7 +6091,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6214,8 +6103,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6226,7 +6114,8 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6237,13 +6126,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6266,16 +6155,21 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="3" t="n"/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -6293,7 +6187,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -6321,12 +6215,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -6341,8 +6230,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6351,19 +6239,19 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">64
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
+      <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6384,7 +6272,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6408,8 +6296,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
@@ -6433,13 +6320,13 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6451,7 +6338,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6471,21 +6358,17 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1185
@@ -6494,13 +6377,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6548,7 +6431,7 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8094
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6560,31 +6443,30 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6619,22 +6501,27 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8181
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
@@ -6652,29 +6539,33 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -6689,7 +6580,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6717,12 +6608,7 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1236
-</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6731,8 +6617,7 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6761,40 +6646,34 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">8306
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6805,19 +6684,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">10896
 </t>
         </is>
       </c>
@@ -6829,16 +6708,11 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11027
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179926
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6847,20 +6721,17 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16620
-</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6877,19 +6748,19 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
@@ -6916,8 +6787,7 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2719
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6928,7 +6798,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6940,13 +6810,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6965,13 +6835,13 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -6989,7 +6859,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -7001,7 +6871,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -7013,7 +6883,7 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -7037,7 +6907,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">16 54
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -729,34 +729,34 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9230
+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -777,64 +777,59 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
@@ -853,7 +848,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -898,77 +898,82 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -977,7 +982,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">565
 </t>
         </is>
       </c>
@@ -1000,10 +1005,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -1015,7 +1025,8 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1068,7 +1079,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -1098,7 +1109,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1110,7 +1121,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1151,7 +1162,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1164,7 +1180,12 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1185,7 +1206,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1197,13 +1218,13 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1215,7 +1236,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1227,7 +1248,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">3004
 </t>
         </is>
       </c>
@@ -1245,19 +1266,20 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1268,7 +1290,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -1280,7 +1302,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1300,31 +1322,37 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">92359
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1340,10 +1368,15 @@
 </t>
         </is>
       </c>
-      <c r="L8" s="3" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1359,7 +1392,12 @@
 </t>
         </is>
       </c>
-      <c r="P8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">306
@@ -1380,38 +1418,43 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">420
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1431,104 +1474,109 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1488
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8871
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">348
+</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4235
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4235
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">11960
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">92551
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1539,25 +1587,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9714
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -1577,7 +1625,7 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1595,7 +1643,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1613,13 +1661,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1667,13 +1715,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1703,13 +1751,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">5 9
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1729,12 +1777,13 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1745,18 +1794,18 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>546</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1791,7 +1840,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -1803,7 +1852,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -1815,21 +1864,41 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1844,10 +1913,15 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1859,7 +1933,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
@@ -1901,7 +1975,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -1919,7 +1993,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1943,38 +2017,39 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="n"/>
+          <t xml:space="preserve">2571
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1994,40 +2069,40 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">60
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -2036,7 +2111,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -2060,13 +2135,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2084,19 +2159,19 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2108,7 +2183,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2120,10 +2195,16 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>7640</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2156,10 +2237,16 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2170,7 +2257,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -2194,13 +2281,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -2218,31 +2305,31 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2260,7 +2347,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2298,7 +2385,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2838
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2326,10 +2413,15 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="3" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -2347,13 +2439,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2383,7 +2475,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2395,7 +2487,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2407,13 +2499,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2430,17 +2522,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10388
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
+          <t xml:space="preserve">1388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2452,19 +2554,18 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t xml:space="preserve">2882
+</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2475,7 +2576,8 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2486,19 +2588,24 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">9094
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8382
+          <t xml:space="preserve">1382
 </t>
         </is>
       </c>
@@ -2516,8 +2623,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2540,7 +2646,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>953</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2551,7 +2657,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2571,7 +2677,7 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2589,13 +2695,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2626,7 +2732,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2638,31 +2744,31 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
@@ -2680,24 +2786,25 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">10685
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">810 8
 </t>
         </is>
       </c>
@@ -2714,51 +2821,56 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2769,14 +2881,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2787,14 +2897,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2805,35 +2913,42 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">007
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">380
+</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2847,12 +2962,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2867,7 +2977,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -2879,7 +2989,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2897,7 +3007,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2915,19 +3025,25 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
@@ -2945,7 +3061,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2975,13 +3091,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2940
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2998,7 +3114,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
@@ -3017,16 +3138,21 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3038,7 +3164,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -3092,13 +3218,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3121,13 +3248,13 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3147,7 +3274,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -3183,19 +3310,18 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3207,7 +3333,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3223,7 +3349,12 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="n"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3238,13 +3369,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -3256,18 +3387,19 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3290,7 +3422,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -3299,13 +3436,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -3341,7 +3478,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3353,7 +3490,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3377,13 +3514,13 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -3401,19 +3538,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3424,7 +3561,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">2549
 </t>
         </is>
       </c>
@@ -3441,10 +3578,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3456,30 +3598,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295
-</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -3491,42 +3633,43 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">1404
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
@@ -3538,41 +3681,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82678
-</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>976</t>
+          <t xml:space="preserve">919
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">11235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">9356
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">6528
 </t>
         </is>
       </c>
@@ -3604,7 +3746,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2375
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3616,49 +3758,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">054
 </t>
         </is>
       </c>
@@ -3670,7 +3807,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2841
 </t>
         </is>
       </c>
@@ -3688,43 +3825,43 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3741,34 +3878,34 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19 4
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3792,35 +3929,36 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">076
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="n"/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3829,13 +3967,12 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
@@ -3847,13 +3984,26 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3867,39 +4017,34 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -3911,7 +4056,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -3933,16 +4078,21 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3966,18 +4116,19 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3995,13 +4146,14 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4017,27 +4169,22 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4049,49 +4196,49 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -4103,7 +4250,8 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -4120,19 +4268,19 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -4148,8 +4296,18 @@
 </t>
         </is>
       </c>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4163,22 +4321,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4190,7 +4353,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
@@ -4202,13 +4365,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4220,19 +4383,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -4262,7 +4425,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
@@ -4274,24 +4437,34 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4305,67 +4478,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -4398,19 +4576,20 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4427,7 +4606,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4456,15 +4635,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13348
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
@@ -4476,60 +4650,57 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
-</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">2800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
-</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>434644</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4564,35 +4735,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>704</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31362
+          <t xml:space="preserve">9162
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>476</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4610,7 +4781,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4634,13 +4805,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4656,15 +4827,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85 2
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4676,13 +4842,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">2051
 </t>
         </is>
       </c>
@@ -4700,16 +4866,16 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">598
@@ -4718,7 +4884,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4742,12 +4908,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4767,11 +4934,15 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4786,8 +4957,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4798,13 +4968,13 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4820,76 +4990,64 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">048
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>548</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">44 128
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4906,19 +5064,19 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4942,7 +5100,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4960,13 +5118,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4984,7 +5142,8 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -4995,19 +5154,19 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5019,7 +5178,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5035,7 +5194,12 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="n"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5052,112 +5216,112 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">482
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -5176,8 +5340,18 @@
 </t>
         </is>
       </c>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5191,33 +5365,28 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5247,13 +5416,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5265,25 +5434,25 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5295,7 +5464,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5313,7 +5482,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">10188
 </t>
         </is>
       </c>
@@ -5323,8 +5492,18 @@
 </t>
         </is>
       </c>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5341,19 +5520,19 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5389,13 +5568,13 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -5425,7 +5604,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -5437,13 +5616,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5467,7 +5646,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -5488,49 +5667,48 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 82
+          <t xml:space="preserve">88218
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4986
+          <t xml:space="preserve">456
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
-</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -5541,54 +5719,53 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">1318
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">10822
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5599,19 +5776,19 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">9981
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -5655,7 +5832,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5673,16 +5850,11 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -5691,13 +5863,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5727,12 +5899,13 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5744,28 +5917,34 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">12790 1
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5779,16 +5958,21 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5799,36 +5983,30 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -5840,50 +6018,51 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n"/>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -5900,11 +6079,15 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5918,94 +6101,94 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1080
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6017,13 +6200,13 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
@@ -6067,32 +6250,31 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -6103,7 +6285,8 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6126,13 +6309,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6142,7 +6325,12 @@
 </t>
         </is>
       </c>
-      <c r="P41" s="3" t="n"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
@@ -6151,7 +6339,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6163,19 +6351,19 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6187,21 +6375,17 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6218,7 +6402,7 @@
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1486
 </t>
         </is>
       </c>
@@ -6230,28 +6414,34 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2201
+</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n"/>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6260,19 +6450,19 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6296,10 +6486,16 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="n"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">520
@@ -6332,13 +6528,13 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6358,41 +6554,46 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1501
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11744
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6401,90 +6602,91 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0250
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6503,51 +6705,52 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6568,31 +6771,31 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">1548
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -6608,7 +6811,12 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6617,7 +6825,8 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6632,7 +6841,12 @@
 </t>
         </is>
       </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6649,54 +6863,55 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11658
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8306
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>951</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">594
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -6708,11 +6923,16 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4990
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6721,56 +6941,64 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11911
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">5179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">15430
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">3929
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111411
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6787,7 +7015,8 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>619</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6798,13 +7027,13 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6826,7 +7055,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72162 8
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
@@ -6841,77 +7075,82 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">5549
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">831
 </t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="Y46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">36
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 54
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -729,104 +729,87 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="U4" s="3" t="n"/>
@@ -850,146 +833,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>565</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1007,146 +966,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1164,146 +1099,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1322,140 +1233,117 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92359
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1474,104 +1362,87 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871
-</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
-</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11960
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92551
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1581,32 +1452,27 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9714
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1625,140 +1491,117 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 9
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1777,8 +1620,7 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1788,8 +1630,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1804,62 +1645,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1874,8 +1705,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1895,8 +1725,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Z11" s="3" t="n"/>
@@ -1915,116 +1744,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -2049,8 +1859,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2069,140 +1878,117 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2221,140 +2007,117 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2373,140 +2136,117 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2524,38 +2264,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2570,26 +2304,22 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9094
-</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2599,26 +2329,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
-</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2628,20 +2354,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2651,14 +2374,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2677,135 +2398,113 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10685
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810 8
-</t>
+          <t>254 1</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2823,14 +2522,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2875,8 +2572,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2891,8 +2587,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2907,8 +2602,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2933,20 +2627,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">007
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2965,140 +2656,117 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2940
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3116,146 +2784,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
+          <t>475</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3274,38 +2918,32 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3315,98 +2953,82 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3424,128 +3046,107 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3555,14 +3156,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3580,38 +3179,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3621,62 +3214,52 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3686,20 +3269,17 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
-</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9356
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -3714,8 +3294,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6528
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3734,135 +3313,113 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3880,63 +3437,53 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 4
-</t>
+          <t>19 2</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">076
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -3961,8 +3508,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3978,8 +3524,7 @@
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3994,14 +3539,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4020,140 +3563,117 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4169,143 +3689,124 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4323,146 +3824,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4480,146 +3957,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4638,20 +4091,17 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
-</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">095
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4661,8 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4672,8 +4121,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4688,14 +4136,12 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4705,38 +4151,32 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
-</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4746,8 +4186,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4757,8 +4196,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162
-</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4781,141 +4219,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2051
-</t>
+          <t>051</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4934,8 +4349,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4945,14 +4359,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4962,39 +4374,33 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -5010,14 +4416,12 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5033,14 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44 128
-</t>
+          <t>91 22</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -5064,140 +4466,117 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5216,140 +4595,117 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5368,140 +4724,117 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5520,134 +4853,112 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5664,29 +4975,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88218
-</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5701,20 +5012,17 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5729,38 +5037,32 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
-</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
-</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5770,32 +5072,27 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
-</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5814,135 +5111,113 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12790 1
-</t>
+          <t>11 1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5960,8 +5235,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5971,14 +5245,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5994,38 +5266,32 @@
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6045,14 +5311,12 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6067,20 +5331,17 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>645</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6104,134 +5365,112 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z40" s="3" t="n"/>
@@ -6250,26 +5489,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -6279,110 +5514,92 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -6402,140 +5619,117 @@
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1486
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6554,140 +5748,117 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11744
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6705,146 +5876,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6860,143 +6007,124 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11658
-</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">594
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
-</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15430
-</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111411
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7015,140 +6143,117 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72162 8
-</t>
+          <t>5 18</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5549
-</t>
+          <t>51 1</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>081 1</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>842</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>254 1</t>
+          <t>90 21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>001</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>136</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>256</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>142</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4400,7 +4400,7 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 22</t>
+          <t>91 191</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4721,7 +4721,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>242</t>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4977,7 +4981,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5052,12 +5056,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5077,12 +5081,12 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>950</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5131,7 +5135,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -5167,7 +5171,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5202,12 +5206,12 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>11 1</t>
+          <t>011 1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -5217,7 +5221,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5489,7 +5493,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5519,7 +5523,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -5599,7 +5603,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -5629,7 +5633,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5758,7 +5762,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5813,7 +5817,7 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
@@ -5823,12 +5827,12 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -5876,12 +5880,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5891,7 +5895,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5901,12 +5905,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5936,7 +5940,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5946,7 +5950,7 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -6009,7 +6013,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6044,7 +6048,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6064,12 +6068,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6089,12 +6093,12 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6114,7 +6118,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6178,7 +6182,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>5 18</t>
+          <t>28 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6193,7 +6197,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>51 1</t>
+          <t>2011 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6203,7 +6207,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6253,7 +6257,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/904/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>318</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>081 1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>892</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>107</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>90 21</t>
+          <t>08 8</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>00</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>572</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4400,7 +4400,7 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>208</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 191</t>
+          <t>00 10</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4721,11 +4721,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>242</t>
@@ -4991,7 +4987,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5061,7 +5057,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>014</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5171,7 +5167,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5191,32 +5187,32 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>05 0</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
           <t>01</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>011 1</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5379,7 +5375,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5454,7 +5450,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5493,7 +5489,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5523,7 +5519,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5578,7 +5574,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5603,7 +5599,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -5847,7 +5843,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>290</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5880,7 +5876,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -5940,7 +5936,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6013,7 +6009,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6048,7 +6044,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6068,7 +6064,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6113,7 +6109,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6182,7 +6178,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>28 08</t>
+          <t>2 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6197,7 +6193,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>2011 0</t>
+          <t>200 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6207,7 +6203,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
